--- a/Usado em ES2N/Grupo1_Controle_de_Contas_a_Pagar_Requisitos_Funcionais rev1509.xlsx
+++ b/Usado em ES2N/Grupo1_Controle_de_Contas_a_Pagar_Requisitos_Funcionais rev1509.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="76">
   <si>
     <t>Código</t>
   </si>
@@ -134,21 +134,9 @@
     <t>Média</t>
   </si>
   <si>
-    <t>RF05</t>
-  </si>
-  <si>
     <t>Fazer Logout</t>
   </si>
   <si>
-    <t>RF06</t>
-  </si>
-  <si>
-    <t>Visualizar Página Inicial</t>
-  </si>
-  <si>
-    <t>Esse requisito apresenta na página inicial as contas prestes a vencer e as contas vencidas, além dos acessos à Agenda e às Contas a Pagar.</t>
-  </si>
-  <si>
     <t>RF07</t>
   </si>
   <si>
@@ -233,9 +221,6 @@
     <t>RF12</t>
   </si>
   <si>
-    <t>Pode executar RF04, RF06,  RF08, RF10, RF11, RF12, RF13, RF14, RF15  (EXTEND)</t>
-  </si>
-  <si>
     <t>Deve executar RF07 (INCLUDE)</t>
   </si>
   <si>
@@ -254,27 +239,6 @@
     <t>Pode executar RF05 e RF14 (EXTEND)</t>
   </si>
   <si>
-    <t>texto aqui</t>
-  </si>
-  <si>
-    <t>Esse requisito permite ao usuário administrador ou funcionário acessar o sistema informando e-mail e senha.</t>
-  </si>
-  <si>
-    <t>Esse requisito permite ao usuário administrador ou funcionário recuperar a senha caso tenha perdido ou esquecido.</t>
-  </si>
-  <si>
-    <t>Esse requisito permite ao usuário administrador ou funcionário encerrar sua sessão no sistema.</t>
-  </si>
-  <si>
-    <t>Esse requisito permite ao usuário administrador ou funcionário acessar seu perfil e as funcionalidades disponibilizadas conforme seu nível de acesso.</t>
-  </si>
-  <si>
-    <t>Esse requisito permite ao usuário administrador cadastrar, alterar ou inativar um ou desativar usuário administrador ou funcionário</t>
-  </si>
-  <si>
-    <t>TIRAR</t>
-  </si>
-  <si>
     <t>PERFIL</t>
   </si>
   <si>
@@ -282,13 +246,37 @@
   </si>
   <si>
     <t>Consultar Contas Receber</t>
+  </si>
+  <si>
+    <t>Administrador</t>
+  </si>
+  <si>
+    <t>Administrador e Funcionário</t>
+  </si>
+  <si>
+    <t>Esse requisito permite ao usuário acessar o sistema informando e-mail e senha.</t>
+  </si>
+  <si>
+    <t>Esse requisito permite ao usuário cadastrar, alterar ou inativar um ou desativar usuário administrador ou funcionário</t>
+  </si>
+  <si>
+    <t>Esse requisito permite ao usuário recuperar a senha caso tenha perdido ou esquecido.</t>
+  </si>
+  <si>
+    <t>Esse requisito permite ao usuário encerrar sua sessão no sistema.</t>
+  </si>
+  <si>
+    <t>Esse requisito permite ao usuário acessar seu perfil e as funcionalidades disponibilizadas conforme seu nível de acesso.</t>
+  </si>
+  <si>
+    <t>RF15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,14 +317,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -346,12 +328,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -405,11 +381,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,17 +593,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultRowHeight="14.55" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="4" width="62" style="3" customWidth="1"/>
-    <col min="5" max="5" width="22.109375" customWidth="1"/>
-    <col min="6" max="6" width="48" style="3" customWidth="1"/>
+    <col min="1" max="1" width="13.98828125" customWidth="1"/>
+    <col min="2" max="2" width="25.9609375" customWidth="1"/>
+    <col min="3" max="4" width="62.015625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.05859375" customWidth="1"/>
+    <col min="6" max="6" width="48.0234375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
@@ -642,7 +613,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="3" spans="1:8" ht="20.6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -650,7 +621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="20.6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="21" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -658,17 +629,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:8" s="3" customFormat="1" ht="64.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" s="3" customFormat="1" ht="64.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>0</v>
       </c>
@@ -678,8 +649,8 @@
       <c r="C9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>66</v>
+      <c r="D9" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>3</v>
@@ -688,23 +659,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="94.4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="66.75" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="E10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="70.8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
@@ -712,17 +685,19 @@
         <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>59</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="70.8" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
@@ -732,7 +707,9 @@
       <c r="C12" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="E12" s="4" t="s">
         <v>18</v>
       </c>
@@ -740,222 +717,227 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="70.8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="E13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:8" s="10" customFormat="1" ht="94.4" x14ac:dyDescent="0.45">
-      <c r="A14" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="9" t="s">
+    <row r="14" spans="1:6" ht="66.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="70.8" x14ac:dyDescent="0.45">
-      <c r="A15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="4"/>
+      <c r="B15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="E15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="70.8" x14ac:dyDescent="0.45">
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" ht="66.75" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="E16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="1:6" ht="70.8" x14ac:dyDescent="0.45">
+      <c r="F16" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="66.75" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="E17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="66.75" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="70.8" x14ac:dyDescent="0.45">
-      <c r="A18" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="B18" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="E18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" ht="94.4" x14ac:dyDescent="0.45">
+      <c r="F18" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="66.75" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="88.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="70.8" x14ac:dyDescent="0.45">
-      <c r="A20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="C20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="4"/>
+        <v>37</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="E20" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="94.4" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="66.75" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="110.25" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="s">
+      <c r="D22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="94.4" x14ac:dyDescent="0.45">
-      <c r="A22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="F22" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" ht="27.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="118" x14ac:dyDescent="0.45">
-      <c r="A23" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="23.3" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="27.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="1"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="4"/>
@@ -963,7 +945,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="4"/>
@@ -971,7 +953,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="4"/>
@@ -979,7 +961,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="4"/>
@@ -987,7 +969,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="4"/>
@@ -995,7 +977,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="4"/>
@@ -1003,7 +985,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="4"/>
@@ -1011,7 +993,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="4"/>
@@ -1019,7 +1001,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="4"/>
@@ -1027,7 +1009,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="4"/>
@@ -1035,7 +1017,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="4"/>
@@ -1043,7 +1025,7 @@
       <c r="E36" s="1"/>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="4"/>
@@ -1051,7 +1033,7 @@
       <c r="E37" s="1"/>
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="4"/>
@@ -1059,7 +1041,7 @@
       <c r="E38" s="1"/>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="4"/>
@@ -1067,7 +1049,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="4"/>
@@ -1075,7 +1057,7 @@
       <c r="E40" s="1"/>
       <c r="F40" s="4"/>
     </row>
-    <row r="41" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="4"/>
@@ -1083,7 +1065,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="4"/>
@@ -1091,7 +1073,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="4"/>
     </row>
-    <row r="43" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="4"/>
@@ -1099,7 +1081,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="4"/>
     </row>
-    <row r="44" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="4"/>
@@ -1107,7 +1089,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="4"/>
@@ -1115,7 +1097,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="4"/>
     </row>
-    <row r="46" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="4"/>
@@ -1123,7 +1105,7 @@
       <c r="E46" s="1"/>
       <c r="F46" s="4"/>
     </row>
-    <row r="47" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="4"/>
@@ -1131,7 +1113,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="4"/>
     </row>
-    <row r="48" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="4"/>
@@ -1139,7 +1121,7 @@
       <c r="E48" s="1"/>
       <c r="F48" s="4"/>
     </row>
-    <row r="49" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="4"/>
@@ -1147,17 +1129,9 @@
       <c r="E49" s="1"/>
       <c r="F49" s="4"/>
     </row>
-    <row r="50" spans="1:6" ht="23.6" x14ac:dyDescent="0.45">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="4"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E10:E23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="E10:E22" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Alta,Média,Baixa"</formula1>
     </dataValidation>
   </dataValidations>
